--- a/build/fees-discounts/chris-round2-answers-source.xlsx
+++ b/build/fees-discounts/chris-round2-answers-source.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Fees &amp; Discounts - Round 2: Four Quick Questions for You</t>
   </si>
@@ -53,6 +53,9 @@
   <si>
     <t>A) Add the warning - the user must see what will happen (total becomes $0.00, the extra becomes a customer credit) and confirm before it saves.
 B) Silent is fine - no warning needed, as long as the credited amount is exact (which it is today).</t>
+  </si>
+  <si>
+    <t>A — already resolved: the warning exists and is spec-required (S6-R12, "the carry is never silent"). It shows before invoicing and before marking the WO reviewed/complete, stating the $0.00 floor, that tax on the taxable base is still owed, and the exact credit amount, and requires confirmation. It intentionally doesn't fire when the adjustment is merely added (nothing committed yet; the add dialog's preview shows the resulting totals). No change needed.</t>
   </si>
   <si>
     <t>Typing 0 as a fee's maximum removes the limit instead of applying it</t>
@@ -69,6 +72,9 @@
 C) Don't allow it - the app should refuse 0 in the maximum box and ask for a real amount (or an empty box).</t>
   </si>
   <si>
+    <t>A — already resolved by spec: S2-R25 says an entered 0 is treated the same as empty, i.e. no maximum. Working as designed; a true $0 cap can only come from legacy data (§5-R6 note), never from the UI. No change needed.</t>
+  </si>
+  <si>
     <t>Very small percentages are quietly rounded up</t>
   </si>
   <si>
@@ -83,6 +89,9 @@
 C) Refuse it - the app should reject anything smaller than 0.01% with a clear message, so the user knowingly picks a valid value.</t>
   </si>
   <si>
+    <t>A -- fully anticipated and expected.</t>
+  </si>
+  <si>
     <t>A processing fee's "minimum amount" is quietly thrown away</t>
   </si>
   <si>
@@ -94,6 +103,9 @@
   <si>
     <t>A) Support it - a processing fee should be able to have a minimum amount, and the app should honor it.
 B) Don't support it - but make that clear: remove/disable the box for processing fees (or show a message) so nothing a user types is ever silently thrown away.</t>
+  </si>
+  <si>
+    <t>B — already resolved by spec: S8-N6 forbids a Processing Fee minimum. Premise doesn't reproduce: there is no minimum-amount field anywhere in the UI, and the API rejects a Processing Fee minimum with an explicit error ("A processing fee cannot have a minimum or maximum cap") — nothing is silently dropped. No change needed.</t>
   </si>
 </sst>
 </file>
@@ -125,7 +137,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -136,6 +148,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -159,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -175,6 +193,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,61 +466,69 @@
       <c r="E5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" ht="150.0" customHeight="1">
       <c r="A6" s="4">
         <v>2.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" ht="150.0" customHeight="1">
       <c r="A7" s="4">
         <v>3.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" ht="150.0" customHeight="1">
       <c r="A8" s="4">
         <v>4.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" ht="14.25" customHeight="1"/>
     <row r="10" ht="14.25" customHeight="1"/>
